--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137326111</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137326112</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137326115</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137326111</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137326112</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137326115</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 40905-2026 artfynd.xlsx
+++ b/artfynd/A 40905-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137326111</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>137326112</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>137326115</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>137326126</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137326109</v>
       </c>
       <c r="B7" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>137326113</v>
       </c>
       <c r="B8" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>137326116</v>
       </c>
       <c r="B9" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>137326118</v>
       </c>
       <c r="B10" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
